--- a/data/RGPV_Result_0105IT2410_1-3.xlsx
+++ b/data/RGPV_Result_0105IT2410_1-3.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -460,9 +460,10 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,15 +544,20 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>RESULT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>SGPA</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>CGPA</t>
         </is>
@@ -636,12 +642,17 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>8.13</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>8.18</t>
         </is>
@@ -723,15 +734,20 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
           <t>Fail in IT305- [T]</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>5.71</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
@@ -816,12 +832,17 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>7.58</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>7.07</t>
         </is>
